--- a/data/trans_orig/IP31KM04_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM04_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>58686</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>47879</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75507</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>50411</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>41242</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>58379</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>44,12%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,1%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>51,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>69037</t>
+          <t>52539</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54045</t>
+          <t>44094</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85342</t>
+          <t>62177</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>119448</t>
+          <t>111225</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103887</t>
+          <t>97585</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140848</t>
+          <t>127334</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64210</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47389</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>75017</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>52,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>61,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>63840</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>55872</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73009</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>55,88%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>48,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>63,9%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67778</t>
+          <t>66059</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51473</t>
+          <t>56421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82770</t>
+          <t>74504</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>131618</t>
+          <t>130269</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110218</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147179</t>
+          <t>143909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>128123</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>113316</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>142965</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>55,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>49,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>61,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>88303</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>76316</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>101418</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>47,45%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>41,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>54,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>133861</t>
+          <t>89266</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>118009</t>
+          <t>77572</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149993</t>
+          <t>100897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>222165</t>
+          <t>217388</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201603</t>
+          <t>197919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>242574</t>
+          <t>235174</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>103118</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>88276</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>117925</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>44,59%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>38,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>51,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>97811</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>84696</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>109798</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>52,55%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>113659</t>
+          <t>91327</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97527</t>
+          <t>79696</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>129511</t>
+          <t>103021</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>211469</t>
+          <t>194445</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191060</t>
+          <t>176659</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>232031</t>
+          <t>213914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>51,94%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52489</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>41376</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64055</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>38,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>60553</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>36157</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>76797</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>32,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,8%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57694</t>
+          <t>55481</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46045</t>
+          <t>45309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71894</t>
+          <t>66069</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>118247</t>
+          <t>107970</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91104</t>
+          <t>93286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139807</t>
+          <t>124936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>114033</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>102467</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>125146</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>68,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>61,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>127696</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>111452</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>152092</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>67,83%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>59,2%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>80,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125395</t>
+          <t>99557</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111195</t>
+          <t>88969</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137044</t>
+          <t>109729</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>253092</t>
+          <t>213590</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>231532</t>
+          <t>196624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>280235</t>
+          <t>228274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>81001</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>70434</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>91899</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>48,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>42,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>55,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>78796</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>68796</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>89735</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>47,89%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>41,82%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>54,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85922</t>
+          <t>79305</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74659</t>
+          <t>68628</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98508</t>
+          <t>91065</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>164718</t>
+          <t>160305</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149547</t>
+          <t>143969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181182</t>
+          <t>174327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>85164</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>74266</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>95731</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>51,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>57,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>85723</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>74784</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>95723</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>52,11%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>45,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>58,18%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>91387</t>
+          <t>84674</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78801</t>
+          <t>72914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102650</t>
+          <t>95351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>177110</t>
+          <t>169839</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160646</t>
+          <t>155817</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192281</t>
+          <t>186175</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,39%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>320299</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>298651</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>346673</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>46,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>50,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>408</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>278064</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>241923</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>304384</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>42,57%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>37,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>346514</t>
+          <t>276591</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>316080</t>
+          <t>254684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>374094</t>
+          <t>298384</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>624578</t>
+          <t>596889</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>579463</t>
+          <t>564640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>663286</t>
+          <t>630113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>366525</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>340151</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>388173</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>53,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>49,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>56,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>375070</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>348750</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>411211</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>57,43%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>53,4%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>62,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>398219</t>
+          <t>341617</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>370639</t>
+          <t>319824</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>428653</t>
+          <t>363524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>773289</t>
+          <t>708142</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>734581</t>
+          <t>674918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>818404</t>
+          <t>740391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
